--- a/data/trans_camb/P38B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P38B-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 1,0</t>
+          <t>-8,13; 1,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 1,08</t>
+          <t>-8,36; 0,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 5,23</t>
+          <t>-4,58; 5,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 3,18</t>
+          <t>-5,01; 4,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 1,56</t>
+          <t>-5,35; 1,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 1,21</t>
+          <t>-5,87; 0,57</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 1,09</t>
+          <t>-8,98; 1,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 1,23</t>
+          <t>-9,19; 0,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 5,99</t>
+          <t>-4,89; 5,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 3,6</t>
+          <t>-5,41; 4,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 1,77</t>
+          <t>-5,86; 1,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,38</t>
+          <t>-6,4; 0,66</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 1,49</t>
+          <t>-7,91; 1,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 0,69</t>
+          <t>-8,9; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 2,38</t>
+          <t>-7,04; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 1,87</t>
+          <t>-7,45; 1,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 0,41</t>
+          <t>-6,1; 0,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,86; -0,29</t>
+          <t>-6,95; -0,33</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 1,74</t>
+          <t>-8,61; 1,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 0,77</t>
+          <t>-9,74; 0,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 2,68</t>
+          <t>-7,63; 2,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 2,11</t>
+          <t>-8,03; 2,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 0,42</t>
+          <t>-6,61; 0,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,44; -0,36</t>
+          <t>-7,56; -0,37</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 6,61</t>
+          <t>-3,34; 5,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-65,21; 4,0</t>
+          <t>-62,07; 4,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 3,6</t>
+          <t>-9,43; 2,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 6,11</t>
+          <t>-4,49; 5,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 4,11</t>
+          <t>-3,12; 4,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 3,47</t>
+          <t>-55,77; 3,49</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 8,04</t>
+          <t>-3,75; 7,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,84; 4,79</t>
+          <t>-73,2; 5,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 4,03</t>
+          <t>-10,24; 3,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 6,88</t>
+          <t>-4,78; 6,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 4,8</t>
+          <t>-3,51; 5,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 4,11</t>
+          <t>-64,8; 3,99</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,62</t>
+          <t>-3,75; 2,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 1,31</t>
+          <t>-6,63; 1,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,42</t>
+          <t>-4,15; 2,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 10,35</t>
+          <t>1,36; 10,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,67</t>
+          <t>-2,96; 1,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 5,75</t>
+          <t>-1,89; 5,29</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 3,16</t>
+          <t>-4,36; 3,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 1,55</t>
+          <t>-7,74; 1,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,87</t>
+          <t>-4,73; 3,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 12,4</t>
+          <t>1,56; 11,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,98</t>
+          <t>-3,4; 1,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 6,82</t>
+          <t>-2,17; 6,29</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 5,28</t>
+          <t>-4,07; 5,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 5,69</t>
+          <t>-5,25; 5,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,15</t>
+          <t>-6,17; 0,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-29,34; 1,64</t>
+          <t>-29,06; 1,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,96</t>
+          <t>-4,82; 0,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 1,87</t>
+          <t>-17,44; 1,5</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,79</t>
+          <t>-5,03; 7,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 7,33</t>
+          <t>-6,37; 7,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 0,17</t>
+          <t>-6,75; 0,41</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,3; 1,83</t>
+          <t>-32,1; 1,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 1,14</t>
+          <t>-5,47; 0,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 2,15</t>
+          <t>-20,21; 1,74</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,93; 18,91</t>
+          <t>1,11; 18,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 13,57</t>
+          <t>-10,56; 14,44</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,35</t>
+          <t>-0,62; 5,15</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,01</t>
+          <t>-7,4; 0,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,75</t>
+          <t>0,29; 6,68</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 0,43</t>
+          <t>-8,52; 0,49</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3,99; 48,88</t>
+          <t>2,13; 45,17</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 34,88</t>
+          <t>-22,04; 36,34</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 6,44</t>
+          <t>-0,74; 6,15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 0,06</t>
+          <t>-8,48; 0,46</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,97</t>
+          <t>0,37; 8,85</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 0,56</t>
+          <t>-10,91; 0,67</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,74</t>
+          <t>-2,12; 1,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-24,61; -0,57</t>
+          <t>-26,34; -0,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,09</t>
+          <t>-2,13; 1,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 1,69</t>
+          <t>-7,71; 1,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,81</t>
+          <t>-1,53; 0,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -0,19</t>
+          <t>-13,57; -0,35</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,14</t>
+          <t>-2,56; 1,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,9; -0,69</t>
+          <t>-31,95; -0,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,25</t>
+          <t>-2,4; 1,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 1,92</t>
+          <t>-8,72; 1,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,96</t>
+          <t>-1,78; 1,01</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -0,22</t>
+          <t>-15,81; -0,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P38B-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-3,55</t>
+          <t>-3,8</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,09</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,31</t>
+          <t>-2,56</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 1,47</t>
+          <t>-8,03; 1,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 0,79</t>
+          <t>-8,8; 0,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 5,16</t>
+          <t>-3,93; 4,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 4,18</t>
+          <t>-5,41; 3,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 1,53</t>
+          <t>-4,92; 1,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,57</t>
+          <t>-5,8; 0,74</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-3,98%</t>
+          <t>-4,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,2%</t>
+          <t>-1,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,58%</t>
+          <t>-2,85%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 1,69</t>
+          <t>-8,86; 1,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 0,91</t>
+          <t>-9,75; 0,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 5,92</t>
+          <t>-4,23; 5,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 4,79</t>
+          <t>-5,84; 3,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 1,72</t>
+          <t>-5,41; 2,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,66</t>
+          <t>-6,37; 0,86</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-4,19</t>
+          <t>-4,51</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,02</t>
+          <t>-3,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,64</t>
+          <t>-3,86</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 1,73</t>
+          <t>-7,85; 1,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 0,59</t>
+          <t>-9,15; -0,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 2,0</t>
+          <t>-7,27; 2,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 1,9</t>
+          <t>-7,58; 1,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 0,65</t>
+          <t>-5,87; 0,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -0,33</t>
+          <t>-7,38; -0,39</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-4,63%</t>
+          <t>-4,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,31%</t>
+          <t>-3,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,02%</t>
+          <t>-4,25%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 1,93</t>
+          <t>-8,44; 1,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 0,67</t>
+          <t>-9,97; -0,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,2</t>
+          <t>-7,82; 2,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 2,1</t>
+          <t>-8,12; 1,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 0,74</t>
+          <t>-6,31; 0,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -0,37</t>
+          <t>-8,08; -0,48</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-29,08</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-23,69</t>
+          <t>1,48</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,89</t>
+          <t>-2,16; 6,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-62,07; 4,9</t>
+          <t>-2,96; 6,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 2,8</t>
+          <t>-8,73; 3,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 5,95</t>
+          <t>-5,17; 4,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 4,35</t>
+          <t>-2,92; 4,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,77; 3,49</t>
+          <t>-2,23; 4,95</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-34,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,35%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 7,15</t>
+          <t>-2,46; 7,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,2; 5,85</t>
+          <t>-3,42; 8,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 3,34</t>
+          <t>-9,33; 3,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 6,7</t>
+          <t>-5,57; 5,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 5,16</t>
+          <t>-3,32; 5,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,8; 3,99</t>
+          <t>-2,53; 5,82</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>-0,61</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 2,77</t>
+          <t>-3,28; 2,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 1,02</t>
+          <t>-6,44; 0,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,87</t>
+          <t>-4,3; 2,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 10,14</t>
+          <t>-0,8; 5,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,63</t>
+          <t>-2,7; 1,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,29</t>
+          <t>-3,02; 1,97</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-3,2%</t>
+          <t>-3,51%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>-0,71%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 3,34</t>
+          <t>-3,79; 3,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 1,24</t>
+          <t>-7,59; 0,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 3,4</t>
+          <t>-4,87; 2,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,56; 11,99</t>
+          <t>-0,92; 6,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,92</t>
+          <t>-3,11; 2,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 6,29</t>
+          <t>-3,49; 2,34</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>-3,96</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-6,83</t>
+          <t>-0,86</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,93</t>
+          <t>-2,14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 5,48</t>
+          <t>-4,05; 5,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 5,76</t>
+          <t>-9,75; 1,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 0,36</t>
+          <t>-6,12; 0,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 1,62</t>
+          <t>-4,08; 2,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,81</t>
+          <t>-5,01; 0,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 1,5</t>
+          <t>-5,11; 0,57</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>-4,93%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-7,6%</t>
+          <t>-0,95%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,57%</t>
+          <t>-2,49%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 7,15</t>
+          <t>-4,87; 6,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 7,4</t>
+          <t>-11,73; 1,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 0,41</t>
+          <t>-6,73; 0,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 1,81</t>
+          <t>-4,43; 2,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 0,98</t>
+          <t>-5,68; 0,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 1,74</t>
+          <t>-5,82; 0,67</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-3,43</t>
+          <t>-5,28</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,09</t>
+          <t>-5,81</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,11; 18,17</t>
+          <t>0,37; 18,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 14,44</t>
+          <t>-13,84; 9,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,15</t>
+          <t>-0,44; 5,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 0,37</t>
+          <t>-9,44; -1,59</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,29; 6,68</t>
+          <t>-0,26; 6,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 0,49</t>
+          <t>-10,11; -1,81</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>-6,69%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-4,05%</t>
+          <t>-6,23%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-5,32%</t>
+          <t>-7,55%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2,13; 45,17</t>
+          <t>0,62; 45,23</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 36,34</t>
+          <t>-29,3; 22,74</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 6,15</t>
+          <t>-0,49; 6,56</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 0,46</t>
+          <t>-11,0; -1,94</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,37; 8,85</t>
+          <t>-0,28; 8,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 0,67</t>
+          <t>-12,81; -2,35</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-7,07</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-3,99</t>
+          <t>-1,59</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,61</t>
+          <t>-2,06; 1,62</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-26,34; -0,53</t>
+          <t>-4,21; 0,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,22</t>
+          <t>-2,21; 1,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 1,47</t>
+          <t>-2,6; 0,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,85</t>
+          <t>-1,56; 0,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-13,57; -0,35</t>
+          <t>-2,91; -0,09</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-8,61%</t>
+          <t>-2,74%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-1,29%</t>
+          <t>-1,14%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-4,69%</t>
+          <t>-1,87%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,98</t>
+          <t>-2,48; 2,03</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-31,95; -0,65</t>
+          <t>-5,1; 0,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,41</t>
+          <t>-2,49; 1,26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 1,68</t>
+          <t>-2,92; 0,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,01</t>
+          <t>-1,82; 0,98</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-15,81; -0,41</t>
+          <t>-3,42; -0,11</t>
         </is>
       </c>
     </row>
